--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA3FA76D-29A0-4FD0-B820-B2C95A777011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1353D51C-A92E-441E-A0A0-22B0F53A449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>Эдгээр бодлогуудыг ашиглан сурагчдад зориулсан тест эсвэл даалгаврын хуудас бэлтгэх үү?</t>
   </si>
   <si>
-    <t>\text{Тэгш өнцөгт } \triangle ABC\text{-ийн } \angle C = 90^\circ \text{ бол } \sin A \text{ харьцааг нэрлэнэ үү. А. } \frac{AC}{AB} \text{ Б. } \frac{BC}{AB} \text{ В. } \frac{BC}{AC} \text{ Г. } \frac{AC}{BC}$ 1</t>
-  </si>
-  <si>
     <t>Асуулт</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>$(1) \ 40, \ (2) \ 25$</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт ABC $C = 90^0$ бол  $sinA$ харьцааг нэрлэнэ үү. А. frac{AC}{AB} \text{ Б. } \frac{BC}{AB} \text{ В. } \frac{BC}{AC} \text{ Г. } \frac{AC}{BC}$ 1</t>
   </si>
 </sst>
 </file>
@@ -506,33 +506,33 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="179.88671875" customWidth="1"/>
+    <col min="1" max="1" width="84.109375" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -540,10 +540,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -551,10 +551,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -562,10 +562,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -573,10 +573,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -584,10 +584,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -595,10 +595,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -606,10 +606,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -617,10 +617,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -628,10 +628,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -639,10 +639,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -650,10 +650,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -661,10 +661,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -672,10 +672,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -683,10 +683,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -694,7 +694,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1353D51C-A92E-441E-A0A0-22B0F53A449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8817B0-D4B4-463E-BDA1-D260A81566B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
-    <t>\text{Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? А. 1:1 Б. 1:2 В. 2:1 Г. 3:1}$ 1</t>
-  </si>
-  <si>
     <t>\text{Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа 4 см ба 6 см хэрчмүүдэд хуваажээ. Хэрэв 8 см бол нөгөө талыг ол. А. 12 см Б. 10 см В. 14 см Г. 16 см}$ 1</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>Тэгш өнцөгт ABC $C = 90^0$ бол  $sinA$ харьцааг нэрлэнэ үү. А. frac{AC}{AB} \text{ Б. } \frac{BC}{AB} \text{ В. } \frac{BC}{AC} \text{ Г. } \frac{AC}{BC}$ 1</t>
+  </si>
+  <si>
+    <t>$\text{Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? $ А. 1:1 Б. 1:2 В. 2:1 Г. 3:1}$ 1</t>
   </si>
 </sst>
 </file>
@@ -512,189 +512,189 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8817B0-D4B4-463E-BDA1-D260A81566B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C60C2C4-709B-485E-8975-C0064698FAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -36,49 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
-  <si>
-    <t>\text{Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа 4 см ба 6 см хэрчмүүдэд хуваажээ. Хэрэв 8 см бол нөгөө талыг ол. А. 12 см Б. 10 см В. 14 см Г. 16 см}$ 1</t>
-  </si>
-  <si>
-    <t>\text{Тэгш өнцөгт гурвалжны катетууд 9 см ба 12 см бол гипотенузын уртыг ол. А. 13 см Б. 15 см В. 17 см Г. 20 см}$ 2</t>
-  </si>
-  <si>
-    <t>\text{Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ? А. 2:1 Б. Гурав хуваана В. Хагаслан хуваана Г. Хуваахгүй}$ 2</t>
-  </si>
-  <si>
-    <t>\text{Тойрогт багтсан өнцөг } 40^\circ \text{ бол түүнд тулсан нумын хэмжээг ол. А. } 20^\circ \text{ Б. } 40^\circ \text{ В. } 80^\circ \text{ Г. } 160^\circ$ 2</t>
-  </si>
-  <si>
-    <t>\text{Тэгш өнцөгт } \triangle ABC\text{-ийн } \angle C = 90^\circ, AC = 12 \text{ см, } \tan A = \frac{3}{4} \text{ бол катетыг ол. А. 8 см Б. 9 см В. 10 см Г. 16 см}$ 2</t>
-  </si>
-  <si>
-    <t> \text{Адил хажуут гурвалжны суурь 16 см, хажуу тал 10 см бол суурьт буусан өндрийг ол. А. 6 см Б. 8 см В. 12 см Г. 5 см}$ 3</t>
-  </si>
-  <si>
-    <t>\text{Тойргийн радиус 13 см. Тойргийн төвөөс 5 см зайд орших хөвчийн уртыг ол. А. 12 см Б. 24 см В. 26 см Г. 10 см}$ 3</t>
-  </si>
-  <si>
-    <t>\text{Тойргийн огтлолцсон хоёр хөвчийн нэг нь 4 см ба 9 см. Нөгөө хөвчийн нэг хэсэг нь 6 см бол нөгөөг ол. А. 4 см Б. 5 см В. 6 см Г. 8 см}$ 3</t>
-  </si>
-  <si>
-    <t>\text{Тойргийн шүргэгч 12 см, огтлогчийн гадна хэсэг 8 см бол огтлогчийн нийт уртыг ол. А. 15 см Б. 16 см В. 18 см Г. 20 см}$ 3</t>
-  </si>
-  <si>
-    <t>\text{Тойргийн гадна оройтой өнцгийн их нум } 110^\circ, \text{ бага нум } 30^\circ \text{ бол өнцгийг ол. А. } 80^\circ \text{ Б. } 140^\circ \text{ В. } 40^\circ \text{ Г. } 70^\circ$ 4</t>
-  </si>
-  <si>
-    <t>\text{Тоононы хөвч төвөөс 9 см, } R=15 \text{ см. (1) } \sqrt{15^2 - 9^2} = \boxed{\quad} \text{ см. (2) Нийт урт: } \boxed{\quad} \times 2 = \boxed{\quad} \text{ см.}$ 4, 5</t>
-  </si>
-  <si>
-    <t>\text{Гэрийн хана 150 см, тооно 230 см, тусгал 60 см. (1) Катетууд: 60 см ба } \boxed{\quad} \text{ см. (2) Унины урт: } \boxed{\quad} \text{ см.}$ 5</t>
-  </si>
-  <si>
-    <t> \text{Хөшөөг харах их нум } 130^\circ, \text{ бага нум } 50^\circ. \text{ (1) Харах өнцөг: } \boxed{\quad}^\circ. \text{ (2) Нумд тулсан өнцөг: } \boxed{\quad}^\circ.$ 5, 6</t>
-  </si>
-  <si>
-    <t>Эдгээр бодлогуудыг ашиглан сурагчдад зориулсан тест эсвэл даалгаврын хуудас бэлтгэх үү?</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>Асуулт</t>
   </si>
@@ -95,35 +53,342 @@
     <t>нэгж5</t>
   </si>
   <si>
-    <t>$\text{ Б}$</t>
-  </si>
-  <si>
-    <t>$\text{ В}$</t>
-  </si>
-  <si>
-    <t>$\text{ А}$</t>
-  </si>
-  <si>
-    <t>$(1) \ 12, \ (2) \ 24$</t>
-  </si>
-  <si>
-    <t>$(1) \ 80, \ (2) \ 100$</t>
-  </si>
-  <si>
-    <t>$(1) \ 40, \ (2) \ 25$</t>
-  </si>
-  <si>
-    <t>Тэгш өнцөгт ABC $C = 90^0$ бол  $sinA$ харьцааг нэрлэнэ үү. А. frac{AC}{AB} \text{ Б. } \frac{BC}{AB} \text{ В. } \frac{BC}{AC} \text{ Г. } \frac{AC}{BC}$ 1</t>
-  </si>
-  <si>
-    <t>$\text{Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? $ А. 1:1 Б. 1:2 В. 2:1 Г. 3:1}$ 1</t>
+    <r>
+      <t xml:space="preserve">Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. $AC/AB$ B. $BC/AB$ C. $BC/AC$ D. $AC/BC$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 1:1 B. 1:2 C. 2:1 D. 3:1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа 4 см ба 6 см хэрчмүүдэд хуваажээ. Хэрэв биссектрис татсан оройд налсан нэг тал нь 8 см бол нөгөө талын уртыг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 12 см B. 10 см C. 14 см D. 16 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тэгш өнцөгт гурвалжны катетууд 9 см ба 12 см бол гипотенузын уртыг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 13 см B. 15 см C. 17 см D. 20 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 2:1 харьцаагаар B. Гурав хуваана C. Хагаслан хуваана D. Хуваахгүй</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойрогт багтсан өнцөг $40^\circ$ бол түүнд тулсан нумын хэмжээг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. $20^\circ$ B. $40^\circ$ C. $80^\circ$ D. $160^\circ$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ, AC = 12$ см, $\tan A = 3/4$ бол нөгөө катетын уртыг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 8 см B. 9 см C. 10 см D. 16 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Адил хажуут гурвалжны суурь 16 см, хажуу тал 10 см бол суурьт буусан өндрийг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 6 см B. 8 см C. 12 см D. 5 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойргийн огтлолцсон хоёр хөвчийн нэг нь 4 см ба 9 см хэрчмүүдэд хуваагджээ. Нөгөө хөвчийн нэг хэсэг нь 6 см бол үлдсэн хэсгийг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 4 см B. 5 см C. 6 см D. 8 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойргийн гадна орших цэгээс тойрогт татсан шүргэгч 12 см, огтлогчийн гадна хэсэг 8 см бол огтлогчийн нийт уртыг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 15 см B. 16 см C. 18 см D. 20 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойргийн гадна оройтой өнцгийн хашиж буй их нум $110^\circ$, бага нум $30^\circ$ бол уг өнцгийн хэмжээг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. $80^\circ$ B. $140^\circ$ C. $40^\circ$ D. $70^\circ$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Монгол гэрийн тооно:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Гэрийн тоононы гол хөндлөвч (хөвч) нь тойргийн төвөөс 9 см зайд оршино. Хэрэв тойргийн радиус 15 см бол: (1) Хөвчийг хагаслан хуваах хэрчмийн урт нь Пифагорын теоремоор $\sqrt{15^2 - 9^2} =$  см байна. (2) Уг хөндлөвч модны нийт урт нь  см болно.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Монгол гэрийн бүтэц:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Гэрийн хананы өндөр 150 см, тоононы өндөр 230 см, унины хэвтээ тусгал 60 см бол: (1) Унины уртыг олохын тулд катетууд нь 60 см ба  см байх тэгш өнцөгт гурвалжин үүснэ. (2) Унины урт нь Пифагорын теоремоор  см болно.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Чингис хааны морьт хөшөө:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Сурагч А цэгээс хөшөөний суурь руу харахад тойргийн гадна оройтой өнцөг үүсэв. (1) Хэрэв харагдах их нум $130^\circ$, бага нум $50^\circ$ бол сурагчийн харах өнцөг  градус байна. (2) Хэрэв сурагч тойргийн шугам дээр очин зогсвол уг $50^\circ$ нумд тулсан өнцөг нь  градус болно.</t>
+    </r>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Тойргийн радиус 13 см. Тойргийн төвөөс 5 см зайд орших хөвчийн уртыг ол. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 12 см</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> B. 24 см C. 26 см D. 10 см</t>
+    </r>
+  </si>
+  <si>
+    <t>quiz5_15.png</t>
+  </si>
+  <si>
+    <t>quiz5_14.png</t>
+  </si>
+  <si>
+    <t>quiz5_3.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +407,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,10 +436,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,198 +781,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04871C1-1734-4EF6-BBF3-64E0ED5AC996}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="84.109375" customWidth="1"/>
+    <col min="1" max="1" width="255.6640625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
       <c r="D16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ADEE74-4801-41C3-8619-8C6514F49631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191E8C9E-D1B1-451D-8C18-BAB2B8EDEB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
   <si>
     <t>Асуулт</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>40,  25</t>
+  </si>
+  <si>
+    <t>Оноо</t>
   </si>
 </sst>
 </file>
@@ -512,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04871C1-1734-4EF6-BBF3-64E0ED5AC996}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="255.6640625" customWidth="1"/>
@@ -520,7 +523,7 @@
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,8 +536,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -544,8 +550,11 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -555,8 +564,11 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -569,8 +581,11 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -580,8 +595,11 @@
       <c r="D5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -591,8 +609,11 @@
       <c r="D6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -602,8 +623,11 @@
       <c r="D7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -613,8 +637,11 @@
       <c r="D8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -624,8 +651,11 @@
       <c r="D9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -635,8 +665,11 @@
       <c r="D10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -646,8 +679,11 @@
       <c r="D11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -657,8 +693,11 @@
       <c r="D12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -668,8 +707,11 @@
       <c r="D13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -679,8 +721,11 @@
       <c r="D14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -693,8 +738,11 @@
       <c r="D15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -705,6 +753,9 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16">
         <v>4</v>
       </c>
     </row>

--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191E8C9E-D1B1-451D-8C18-BAB2B8EDEB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190FBAAB-120C-416E-806D-ED57A9E0FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>quiz5_3.png</t>
   </si>
   <si>
-    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү. A. $AC/AB$ B. $BC/AB$ C. $BC/AC$ D. $AC/BC$</t>
-  </si>
-  <si>
     <t>Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? A. 1:1 B. 1:2 C. 2:1 D. 3:1</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>Оноо</t>
+  </si>
+  <si>
+    <t>$Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү.$           A. $AC/AB$ B. $BC/AB$ C. $BC/AC$ D. $AC/BC$</t>
   </si>
 </sst>
 </file>
@@ -537,12 +537,12 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -713,10 +713,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -727,10 +727,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -744,10 +744,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>

--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190FBAAB-120C-416E-806D-ED57A9E0FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1CD600-A172-493E-BED1-8C6B285001CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -71,48 +71,12 @@
     <t>quiz5_3.png</t>
   </si>
   <si>
-    <t>Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? A. 1:1 B. 1:2 C. 2:1 D. 3:1</t>
-  </si>
-  <si>
-    <t>Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа 4 см ба 6 см хэрчмүүдэд хуваажээ. Хэрэв биссектрис татсан оройд налсан нэг тал нь 8 см бол нөгөө талын уртыг ол. A. 12 см B. 10 см C. 14 см D. 16 см</t>
-  </si>
-  <si>
-    <t>Тэгш өнцөгт гурвалжны катетууд 9 см ба 12 см бол гипотенузын уртыг ол. A. 13 см B. 15 см C. 17 см D. 20 см</t>
-  </si>
-  <si>
-    <t>Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ? A. 2:1 харьцаагаар B. Гурав хуваана C. Хагаслан хуваана D. Хуваахгүй</t>
-  </si>
-  <si>
     <t>Тойрогт багтсан өнцөг $40^\circ$ бол түүнд тулсан нумын хэмжээг ол. A. $20^\circ$ B. $40^\circ$ C. $80^\circ$ D. $160^\circ$</t>
   </si>
   <si>
-    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ, AC = 12$ см, $\tan A = 3/4$ бол нөгөө катетын уртыг ол. A. 8 см B. 9 см C. 10 см D. 16 см</t>
-  </si>
-  <si>
-    <t>Адил хажуут гурвалжны суурь 16 см, хажуу тал 10 см бол суурьт буусан өндрийг ол. A. 6 см B. 8 см C. 12 см D. 5 см</t>
-  </si>
-  <si>
-    <t>Тойргийн радиус 13 см. Тойргийн төвөөс 5 см зайд орших хөвчийн уртыг ол. A. 12 см B. 24 см C. 26 см D. 10 см</t>
-  </si>
-  <si>
-    <t>Тойргийн огтлолцсон хоёр хөвчийн нэг нь 4 см ба 9 см хэрчмүүдэд хуваагджээ. Нөгөө хөвчийн нэг хэсэг нь 6 см бол үлдсэн хэсгийг ол. A. 4 см B. 5 см C. 6 см D. 8 см</t>
-  </si>
-  <si>
-    <t>Тойргийн гадна орших цэгээс тойрогт татсан шүргэгч 12 см, огтлогчийн гадна хэсэг 8 см бол огтлогчийн нийт уртыг ол. A. 15 см B. 16 см C. 18 см D. 20 см</t>
-  </si>
-  <si>
     <t>Тойргийн гадна оройтой өнцгийн хашиж буй их нум $110^\circ$, бага нум $30^\circ$ бол уг өнцгийн хэмжээг ол. A. $80^\circ$ B. $140^\circ$ C. $40^\circ$ D. $70^\circ$</t>
   </si>
   <si>
-    <t>Монгол гэрийн тооно: Гэрийн тоононы гол хөндлөвч (хөвч) нь тойргийн төвөөс 9 см зайд оршино. Хэрэв тойргийн радиус 15 см бол: (1) Хөвчийг хагаслан хуваах хэрчмийн урт нь Пифагорын теоремоор $\sqrt{15^2 - 9^2} =$  см байна. (2) Уг хөндлөвч модны нийт урт нь  см болно.</t>
-  </si>
-  <si>
-    <t>Монгол гэрийн бүтэц: Гэрийн хананы өндөр 150 см, тоононы өндөр 230 см, унины хэвтээ тусгал 60 см бол: (1) Унины уртыг олохын тулд катетууд нь 60 см ба  см байх тэгш өнцөгт гурвалжин үүснэ. (2) Унины урт нь Пифагорын теоремоор  см болно.</t>
-  </si>
-  <si>
-    <t>Чингис хааны морьт хөшөө: Сурагч А цэгээс хөшөөний суурь руу харахад тойргийн гадна оройтой өнцөг үүсэв. (1) Хэрэв харагдах их нум $130^\circ$, бага нум $50^\circ$ бол сурагчийн харах өнцөг  градус байна. (2) Хэрэв сурагч тойргийн шугам дээр очин зогсвол уг $50^\circ$ нумд тулсан өнцөг нь  градус болно.</t>
-  </si>
-  <si>
     <t>12, 24</t>
   </si>
   <si>
@@ -125,14 +89,113 @@
     <t>Оноо</t>
   </si>
   <si>
-    <t>$Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү.$           A. $AC/AB$ B. $BC/AB$ C. $BC/AC$ D. $AC/BC$</t>
+    <t>Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? A. $1:1$ B. $1:2$ C. $2:1$ D. $3:1$</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү. A. $\frac{AC}{AB}$ B. $\frac{BC}{AB}$ C. $\frac{BC}{AC}$ D. $\frac{AC}{BC}$</t>
+  </si>
+  <si>
+    <t>Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа $4$ см ба $6$ см хэрчмүүдэд хуваажээ. Хэрэв биссектрис татсан оройд налсан нэг тал нь $8$ см бол нөгөө талын уртыг ол. A. $12$ см B. $10$ см C. $14$ см D. $16$ см</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт гурвалжны катетууд $9$ см ба $12$ см бол гипотенузын уртыг ол. A. $13$ см B. $15$ см C. $17$ см D. $20$ см</t>
+  </si>
+  <si>
+    <t>Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ? A. $2:1$ харьцаагаар B. Гурав хуваана C. Хагаслан хуваана D. Хуваахгүй</t>
+  </si>
+  <si>
+    <r>
+      <t>Монгол гэрийн тооно:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Гэрийн тоононы гол хөндлөвч (хөвч) нь тойргийн төвөөс $9$ см зайд оршино. Хэрэв тойргийн радиус $15$ см бол:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1) Хөвчийг хагаслан хуваах хэрчмийн урт нь Пифагорын теоремоор $\sqrt{15^2 - 9^2} = \boxed{\phantom{55}}$ см байна. (2) Уг хөндлөвч модны нийт урт нь $\boxed{\phantom{55}} \times 2 = \boxed{\phantom{55}}$ см болно.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Монгол гэрийн бүтэц:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Малчин Бат гэрийнхээ хананаас тооно хүртэлх унины уртыг тооцоолов. Гэрийн хананы өндөр $150$ см, тоононы өндөр $230$ см. Хэрэв унины хэвтээ тусгал $60$ см бол:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1) Унины уртыг олохын тулд катетууд нь $60$ см ба $\boxed{\phantom{55}}$ см байх тэгш өнцөгт гурвалжин үүснэ. (2) Унины урт нь Пифагорын теоремоор $\boxed{\phantom{55}}$ см болно.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Чингис хааны морьт хөшөө:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Цонжин болдог дахь хөшөөг ажиглаж буй сурагч А цэгээс хөшөөний суурь рүү харахад тойргийн гадна оройтой өнцөг үүсэв.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (1) Хэрэв харагдах их нум $130^\circ$, бага нум $50^\circ$ бол сурагчийн харах өнцөг $\boxed{\phantom{55}}$ градус байна. (2) Хэрэв сурагч тойргийн шугам дээр очин зогсвол уг $50^\circ$ нумд тулсан өнцөг нь $\boxed{\phantom{55}}$ градус болно.</t>
+    </r>
+  </si>
+  <si>
+    <t>Тойргийн гадна орших цэгээс тойрогт татсан шүргэгч $12$ см, огтлогчийн гадна хэсэг $8$ см бол огтлогчийн нийт уртыг ол. A. $15$ см B. $16$ см C. $18$ см D. $20$ см</t>
+  </si>
+  <si>
+    <t>Тойргийн огтлолцсон хоёр хөвчийн нэг нь $4$ см ба $9$ см хэрчмүүдэд хуваагджээ. Нөгөө хөвчийн нэг хэсэг нь $6$ см бол үлдсэн хэсгийг ол. A. $4$ см B. $5$ см C. $6$ см D. $8$ см</t>
+  </si>
+  <si>
+    <t>Тойргийн радиус $13$ см. Тойргийн төвөөс $5$ см зайд орших хөвчийн уртыг ол. A. $12$ см B. $24$ см C. $26$ см D. $10$ см</t>
+  </si>
+  <si>
+    <t>Адил хажуут гурвалжны суурь $16$ см, хажуу тал $10$ см бол суурьт буусан өндрийг ол. A. $6$ см B. $8$ см C. $12$ см D. $5$ см</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ, AC = 12$ см, $\tan A = \frac{3}{4}$ бол катетын уртыг ол. A. $8$ см B. $9$ см C. $10$ см D. $16$ см</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +214,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -173,13 +243,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04871C1-1734-4EF6-BBF3-64E0ED5AC996}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="255.6640625" customWidth="1"/>
@@ -537,12 +610,12 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -556,7 +629,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -570,7 +643,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -587,7 +660,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -601,7 +674,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -615,7 +688,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -629,7 +702,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -643,7 +716,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -657,7 +730,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -671,7 +744,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -685,7 +758,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -699,7 +772,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -712,11 +785,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -726,11 +799,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -743,11 +816,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -758,9 +831,16 @@
       <c r="E16">
         <v>4</v>
       </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/quiz_5_a.xlsx
+++ b/quiz_5_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1CD600-A172-493E-BED1-8C6B285001CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844BDC9B-71CC-4A12-A73E-C3FE027820F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{90F7A116-932E-4EC7-8C83-F23928794BAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>Асуулт</t>
   </si>
@@ -71,12 +71,6 @@
     <t>quiz5_3.png</t>
   </si>
   <si>
-    <t>Тойрогт багтсан өнцөг $40^\circ$ бол түүнд тулсан нумын хэмжээг ол. A. $20^\circ$ B. $40^\circ$ C. $80^\circ$ D. $160^\circ$</t>
-  </si>
-  <si>
-    <t>Тойргийн гадна оройтой өнцгийн хашиж буй их нум $110^\circ$, бага нум $30^\circ$ бол уг өнцгийн хэмжээг ол. A. $80^\circ$ B. $140^\circ$ C. $40^\circ$ D. $70^\circ$</t>
-  </si>
-  <si>
     <t>12, 24</t>
   </si>
   <si>
@@ -89,106 +83,96 @@
     <t>Оноо</t>
   </si>
   <si>
-    <t>Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ? A. $1:1$ B. $1:2$ C. $2:1$ D. $3:1$</t>
-  </si>
-  <si>
-    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ$ бол $\sin A$ харьцааг нэрлэнэ үү. A. $\frac{AC}{AB}$ B. $\frac{BC}{AB}$ C. $\frac{BC}{AC}$ D. $\frac{AC}{BC}$</t>
-  </si>
-  <si>
-    <t>Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа $4$ см ба $6$ см хэрчмүүдэд хуваажээ. Хэрэв биссектрис татсан оройд налсан нэг тал нь $8$ см бол нөгөө талын уртыг ол. A. $12$ см B. $10$ см C. $14$ см D. $16$ см</t>
-  </si>
-  <si>
-    <t>Тэгш өнцөгт гурвалжны катетууд $9$ см ба $12$ см бол гипотенузын уртыг ол. A. $13$ см B. $15$ см C. $17$ см D. $20$ см</t>
-  </si>
-  <si>
-    <t>Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ? A. $2:1$ харьцаагаар B. Гурав хуваана C. Хагаслан хуваана D. Хуваахгүй</t>
-  </si>
-  <si>
-    <r>
-      <t>Монгол гэрийн тооно:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Гэрийн тоононы гол хөндлөвч (хөвч) нь тойргийн төвөөс $9$ см зайд оршино. Хэрэв тойргийн радиус $15$ см бол:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1) Хөвчийг хагаслан хуваах хэрчмийн урт нь Пифагорын теоремоор $\sqrt{15^2 - 9^2} = \boxed{\phantom{55}}$ см байна. (2) Уг хөндлөвч модны нийт урт нь $\boxed{\phantom{55}} \times 2 = \boxed{\phantom{55}}$ см болно.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Монгол гэрийн бүтэц:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Малчин Бат гэрийнхээ хананаас тооно хүртэлх унины уртыг тооцоолов. Гэрийн хананы өндөр $150$ см, тоононы өндөр $230$ см. Хэрэв унины хэвтээ тусгал $60$ см бол:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1) Унины уртыг олохын тулд катетууд нь $60$ см ба $\boxed{\phantom{55}}$ см байх тэгш өнцөгт гурвалжин үүснэ. (2) Унины урт нь Пифагорын теоремоор $\boxed{\phantom{55}}$ см болно.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Чингис хааны морьт хөшөө:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Цонжин болдог дахь хөшөөг ажиглаж буй сурагч А цэгээс хөшөөний суурь рүү харахад тойргийн гадна оройтой өнцөг үүсэв.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1) Хэрэв харагдах их нум $130^\circ$, бага нум $50^\circ$ бол сурагчийн харах өнцөг $\boxed{\phantom{55}}$ градус байна. (2) Хэрэв сурагч тойргийн шугам дээр очин зогсвол уг $50^\circ$ нумд тулсан өнцөг нь $\boxed{\phantom{55}}$ градус болно.</t>
-    </r>
-  </si>
-  <si>
-    <t>Тойргийн гадна орших цэгээс тойрогт татсан шүргэгч $12$ см, огтлогчийн гадна хэсэг $8$ см бол огтлогчийн нийт уртыг ол. A. $15$ см B. $16$ см C. $18$ см D. $20$ см</t>
-  </si>
-  <si>
-    <t>Тойргийн огтлолцсон хоёр хөвчийн нэг нь $4$ см ба $9$ см хэрчмүүдэд хуваагджээ. Нөгөө хөвчийн нэг хэсэг нь $6$ см бол үлдсэн хэсгийг ол. A. $4$ см B. $5$ см C. $6$ см D. $8$ см</t>
-  </si>
-  <si>
-    <t>Тойргийн радиус $13$ см. Тойргийн төвөөс $5$ см зайд орших хөвчийн уртыг ол. A. $12$ см B. $24$ см C. $26$ см D. $10$ см</t>
-  </si>
-  <si>
-    <t>Адил хажуут гурвалжны суурь $16$ см, хажуу тал $10$ см бол суурьт буусан өндрийг ол. A. $6$ см B. $8$ см C. $12$ см D. $5$ см</t>
-  </si>
-  <si>
-    <t>Тэгш өнцөгт $\triangle ABC$-ийн $\angle C = 90^\circ, AC = 12$ см, $\tan A = \frac{3}{4}$ бол катетын уртыг ол. A. $8$ см B. $9$ см C. $10$ см D. $16$ см</t>
+    <t>Тэгш өнцөгт \( \triangle ABC \)-ийн \( \angle C = 90^\circ \) бол \( \sin A \) харьцааг нэрлэнэ үү.
+   A. \( \frac{AC}{AB} \)
+   B. \( \frac{BC}{AB} \)
+   C. \( \frac{BC}{AC} \)
+   D. \( \frac{AC}{BC} \)</t>
+  </si>
+  <si>
+    <t>Гурвалжны медианууд огтлолцлын цэгээрээ оройгоосоо тоолбол ямар харьцаагаар хуваагддаг вэ?
+   A. 1:1
+   B. 1:2
+   C. 2:1
+   D. 3:1</t>
+  </si>
+  <si>
+    <t>Гурвалжны нэг оройгоос татсан биссектрис эсрэг талаа 4 см ба 6 см хэрчмүүдэд хуваажээ. Хэрэв биссектрис татсан оройд налсан нэг тал нь 8 см бол нөгөө талын уртыг ол.
+   A. 12 см
+   B. 10 см
+   C. 14 см
+   D. 16 см</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт гурвалжны катетууд 9 см ба 12 см бол гипотенузын уртыг ол.
+   A. 13 см
+   B. 15 см
+   C. 17 см
+   D. 20 см</t>
+  </si>
+  <si>
+    <t>Тойргийн төвөөс хөвчид буусан перпендикуляр нь уг хөвчийг хэрхэн хуваадаг вэ?
+   A. 2:1 харьцаагаар
+   B. Гурав хуваана
+   C. Хагаслан хуваана
+   D. Хуваахгүй</t>
+  </si>
+  <si>
+    <t>Тойрогт багтсан өнцөг 40\(^\circ\) бол түүнд тулсан нумын хэмжээг ол.
+   A. 20\(^\circ\)
+   B. 40\(^\circ\)
+   C. 80\(^\circ\)
+   D. 160\(^\circ\)</t>
+  </si>
+  <si>
+    <t>Адил хажуут гурвалжны суурь 16 см, хажуу тал 10 см бол суурьт буусан өндрийг ол.
+   A. 6 см
+   B. 8 см
+   C. 12 см
+   D. 5 см</t>
+  </si>
+  <si>
+    <t>Тойргийн радиус 13 см. Тойргийн төвөөс 5 см зайд орших хөвчийн уртыг ол.
+   A. 12 см
+   B. 24 см
+   C. 26 см
+   D. 10 см</t>
+  </si>
+  <si>
+    <t>Тойргийн огтлолцсон хоёр хөвчийн нэг нь 4 см ба 9 см хэрчмүүдэд хуваагджээ. Нөгөө хөвчийн нэг хэсэг нь 6 см бол үлдсэн хэсгийг ол.
+    A. 4 см
+    B. 5 см
+    C. 6 см
+    D. 8 см</t>
+  </si>
+  <si>
+    <t>Тойргийн гадна орших цэгээс тойрогт татсан шүргэгч 12 см, огтлогчийн гадна хэсэг 8 см бол огтлогчийн нийт уртыг ол.
+    A. 15 см
+    B. 16 см
+    C. 18 см
+    D. 20 см</t>
+  </si>
+  <si>
+    <t>Тойргийн гадна оройтой өнцгийн хашиж буй их нум 110\(^\circ\), бага нум 30\(^\circ\) бол уг өнцгийн хэмжээг ол.
+    A. 80\(^\circ\)
+    B. 140\(^\circ\)
+    C. 40\(^\circ\)
+    D. 70\(^\circ\)</t>
+  </si>
+  <si>
+    <t>Монгол гэрийн тооно:** Гэрийн тоононы гол хөндлөвч (хөвч) нь тойргийн төвөөс 9 см зайд оршино. Хэрэв тойргийн радиус 15 см бол:
+    - (1) Хөвчийг хагаслан хуваах хэрчмийн урт нь Пифагорын теоремоор \( \sqrt{15^2 - 9^2} = \boxed{12} \) см байна.
+    - (2) Уг хөндлөвч модны нийт урт нь \( \boxed{12} \times 2 = \boxed{24} \) см болно.</t>
+  </si>
+  <si>
+    <t>Монгол гэрийн бүтэц:** Малчин Бат гэрийнхээ хананаас тооно хүртэлх унины уртыг тооцоолов. Гэрийн хананы өндөр 150 см, тоононы өндөр 230 см. Хэрэв унины хэвтээ тусгал 60 см бол:
+    - (1) Унины уртыг олохын тулд катетууд нь 60 см ба \( \boxed{80} \) см (учир нь \( 230 - 150 = 80 \)) байх тэгш өнцөгт гурвалжин үүснэ.
+    - (2) Унины урт нь Пифагорын теоремоор \( \boxed{100} \) см болно.</t>
+  </si>
+  <si>
+    <t>Чингис хааны морьт хөшөө:** Цонжин болдог дахь хөшөөг ажиглаж буй сурагч А цэгээс хөшөөний суурь рүү харахад тойргийн гадна оройтой өнцөг үүсэв.
+    - (1) Хэрэв харагдах их нум 130\(^\circ\), бага нум 50\(^\circ\) бол сурагчийн харах өнцөг \( \boxed{40} \) градус байна.
+    - (2) Хэрэв сурагч тойргийн шугам дээр очин зогсвол уг 50\(^\circ\) нумд тулсан өнцөг нь \( \boxed{25} \) градус болно.</t>
   </si>
 </sst>
 </file>
@@ -243,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -251,8 +235,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,12 +597,12 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -627,9 +614,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
+    <row r="3" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -641,9 +628,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
+    <row r="4" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -658,9 +645,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
+    <row r="5" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -672,9 +659,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
+    <row r="6" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -686,9 +673,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
+    <row r="7" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -700,9 +687,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>29</v>
+    <row r="8" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -714,9 +701,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
+    <row r="9" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -728,9 +715,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
+    <row r="10" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -742,9 +729,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
+    <row r="11" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -756,9 +743,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
+    <row r="12" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -770,9 +757,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
+    <row r="13" spans="1:5" ht="69" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -784,12 +771,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>22</v>
+    <row r="14" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -798,12 +785,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
+    <row r="15" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -815,12 +802,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>24</v>
+    <row r="16" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
